--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484093_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484093_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A. AMABILINO PEREZ</t>
+          <t>M. GONZALEZ DE UBIETA BELLO</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.5789</v>
+        <v>5.8615</v>
       </c>
       <c r="E2" t="n">
-        <v>7.2316</v>
+        <v>7.7499</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.6527</v>
+        <v>-1.8884</v>
       </c>
       <c r="G2" t="n">
-        <v>4.0975</v>
+        <v>2.1964</v>
       </c>
       <c r="H2" t="n">
-        <v>2.0518</v>
+        <v>-0.3935</v>
       </c>
       <c r="I2" t="n">
-        <v>2.0457</v>
+        <v>2.5898</v>
       </c>
       <c r="J2" t="n">
-        <v>4.5652</v>
+        <v>4.8819</v>
       </c>
       <c r="K2" t="n">
-        <v>2.552</v>
+        <v>0.9837</v>
       </c>
       <c r="L2" t="n">
-        <v>2.0132</v>
+        <v>3.8982</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.4677</v>
+        <v>-2.6855</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.5002</v>
+        <v>-1.3771</v>
       </c>
       <c r="O2" t="n">
-        <v>0.0325</v>
+        <v>-1.3084</v>
       </c>
       <c r="P2" t="n">
-        <v>1.5871</v>
+        <v>2.7774</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.9838</v>
+        <v>-0.9919</v>
       </c>
       <c r="R2" t="n">
-        <v>3.5709</v>
+        <v>3.7693</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.2408</v>
+        <v>-2.1284</v>
       </c>
       <c r="T2" t="n">
-        <v>0.4989</v>
+        <v>-0.3626</v>
       </c>
       <c r="U2" t="n">
-        <v>-1.7397</v>
+        <v>-1.7658</v>
       </c>
       <c r="V2" t="n">
-        <v>1.1352</v>
+        <v>3.0162</v>
       </c>
       <c r="W2" t="n">
-        <v>4.1513</v>
+        <v>4.2226</v>
       </c>
       <c r="X2" t="n">
-        <v>-3.0162</v>
+        <v>-1.2065</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>M. GONZALEZ DE UBIETA BELLO</t>
+          <t>A. AMABILINO PEREZ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.1309</v>
+        <v>5.149</v>
       </c>
       <c r="E3" t="n">
-        <v>7.0754</v>
+        <v>6.8858</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.9446</v>
+        <v>-1.7368</v>
       </c>
       <c r="G3" t="n">
-        <v>2.1964</v>
+        <v>4.0975</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.3935</v>
+        <v>2.0518</v>
       </c>
       <c r="I3" t="n">
-        <v>2.5898</v>
+        <v>2.0457</v>
       </c>
       <c r="J3" t="n">
-        <v>4.8819</v>
+        <v>4.5652</v>
       </c>
       <c r="K3" t="n">
-        <v>0.9837</v>
+        <v>2.552</v>
       </c>
       <c r="L3" t="n">
-        <v>3.8982</v>
+        <v>2.0132</v>
       </c>
       <c r="M3" t="n">
-        <v>-2.6855</v>
+        <v>-0.4677</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.3771</v>
+        <v>-0.5002</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.3084</v>
+        <v>0.0325</v>
       </c>
       <c r="P3" t="n">
-        <v>2.7774</v>
+        <v>1.5871</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.9919</v>
+        <v>-1.9838</v>
       </c>
       <c r="R3" t="n">
-        <v>3.7693</v>
+        <v>3.5709</v>
       </c>
       <c r="S3" t="n">
-        <v>-2.8591</v>
+        <v>-1.6708</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.0372</v>
+        <v>0.1531</v>
       </c>
       <c r="U3" t="n">
-        <v>-1.8219</v>
+        <v>-1.8239</v>
       </c>
       <c r="V3" t="n">
-        <v>3.0162</v>
+        <v>1.1352</v>
       </c>
       <c r="W3" t="n">
-        <v>4.2226</v>
+        <v>4.1513</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.2065</v>
+        <v>-3.0162</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.747</v>
+        <v>1.5531</v>
       </c>
       <c r="E4" t="n">
-        <v>1.3688</v>
+        <v>1.0627</v>
       </c>
       <c r="F4" t="n">
-        <v>0.3782</v>
+        <v>0.4904</v>
       </c>
       <c r="G4" t="n">
         <v>0.0742</v>
@@ -766,13 +766,13 @@
         <v>1.7855</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.0531</v>
+        <v>-1.247</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0567</v>
+        <v>-0.2493</v>
       </c>
       <c r="U4" t="n">
-        <v>-1.1099</v>
+        <v>-0.9977</v>
       </c>
       <c r="V4" t="n">
         <v>0.9405</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.6291</v>
+        <v>0.8893</v>
       </c>
       <c r="E5" t="n">
-        <v>1.5536</v>
+        <v>1.7576</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.9244</v>
+        <v>-0.8683</v>
       </c>
       <c r="G5" t="n">
         <v>1.2954</v>
@@ -844,13 +844,13 @@
         <v>1.7855</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.6824</v>
+        <v>-0.4223</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.1757</v>
+        <v>0.0284</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.5067</v>
+        <v>-0.4506</v>
       </c>
       <c r="V5" t="n">
         <v>1.2065</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>C. BONAZEBI LOUSSAKOU</t>
+          <t>A. PILAN PERET</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.0166</v>
+        <v>-0.4797</v>
       </c>
       <c r="E6" t="n">
-        <v>1.2463</v>
+        <v>-0.1671</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.2629</v>
+        <v>-0.3125</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.4266</v>
+        <v>1.7587</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.7413</v>
+        <v>0.458</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.6853</v>
+        <v>1.3007</v>
       </c>
       <c r="J6" t="n">
-        <v>0.3619</v>
+        <v>1.6086</v>
       </c>
       <c r="K6" t="n">
-        <v>0.121</v>
+        <v>-0.3268</v>
       </c>
       <c r="L6" t="n">
-        <v>0.241</v>
+        <v>1.9354</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.7885</v>
+        <v>0.1502</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.8623</v>
+        <v>0.7849</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.9263</v>
+        <v>-0.6347</v>
       </c>
       <c r="P6" t="n">
-        <v>1.3887</v>
+        <v>0.1984</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-2.9758</v>
       </c>
       <c r="R6" t="n">
-        <v>1.3887</v>
+        <v>3.1741</v>
       </c>
       <c r="S6" t="n">
-        <v>0.5533</v>
+        <v>-2.9688</v>
       </c>
       <c r="T6" t="n">
-        <v>0.8843</v>
+        <v>-0.5384</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.3311</v>
+        <v>-2.4304</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.532</v>
+        <v>0.532</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.7384</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.532</v>
+        <v>-1.2065</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>P. FEIXA MORANCHO</t>
+          <t>C. BONAZEBI LOUSSAKOU</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.1873</v>
+        <v>-0.6124000000000001</v>
       </c>
       <c r="E7" t="n">
-        <v>1.6264</v>
+        <v>0.5944</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.8138</v>
+        <v>-1.2068</v>
       </c>
       <c r="G7" t="n">
-        <v>3.2825</v>
+        <v>-1.4266</v>
       </c>
       <c r="H7" t="n">
-        <v>4.0818</v>
+        <v>-0.7413</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.7993</v>
+        <v>-0.6853</v>
       </c>
       <c r="J7" t="n">
-        <v>3.3665</v>
+        <v>0.3619</v>
       </c>
       <c r="K7" t="n">
-        <v>3.246</v>
+        <v>0.121</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1205</v>
+        <v>0.241</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.08400000000000001</v>
+        <v>-1.7885</v>
       </c>
       <c r="N7" t="n">
-        <v>0.8358</v>
+        <v>-0.8623</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.9198</v>
+        <v>-0.9263</v>
       </c>
       <c r="P7" t="n">
-        <v>0.1984</v>
+        <v>1.3887</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.9838</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>2.1822</v>
+        <v>1.3887</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.1201</v>
+        <v>-0.0425</v>
       </c>
       <c r="T7" t="n">
-        <v>0.2438</v>
+        <v>0.2325</v>
       </c>
       <c r="U7" t="n">
-        <v>-1.3639</v>
+        <v>-0.275</v>
       </c>
       <c r="V7" t="n">
-        <v>-3.5481</v>
+        <v>-0.532</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-3.5481</v>
+        <v>-0.532</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. PILAN PERET</t>
+          <t>R. SOLIVELLES MENDEZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.3047</v>
+        <v>-1.671</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.7396</v>
+        <v>-2.0727</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.5649999999999999</v>
+        <v>0.4017</v>
       </c>
       <c r="G8" t="n">
-        <v>1.7587</v>
+        <v>0.3356</v>
       </c>
       <c r="H8" t="n">
-        <v>0.458</v>
+        <v>0.7657</v>
       </c>
       <c r="I8" t="n">
-        <v>1.3007</v>
+        <v>-0.4302</v>
       </c>
       <c r="J8" t="n">
-        <v>1.6086</v>
+        <v>0.4949</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.3268</v>
+        <v>0.0053</v>
       </c>
       <c r="L8" t="n">
-        <v>1.9354</v>
+        <v>0.4896</v>
       </c>
       <c r="M8" t="n">
-        <v>0.1502</v>
+        <v>-0.1593</v>
       </c>
       <c r="N8" t="n">
-        <v>0.7849</v>
+        <v>0.7604</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.6347</v>
+        <v>-0.9198</v>
       </c>
       <c r="P8" t="n">
-        <v>0.1984</v>
+        <v>-0.3968</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.9758</v>
+        <v>-1.9838</v>
       </c>
       <c r="R8" t="n">
-        <v>3.1741</v>
+        <v>1.5871</v>
       </c>
       <c r="S8" t="n">
-        <v>-3.7937</v>
+        <v>-1.947</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.1109</v>
+        <v>-0.5838</v>
       </c>
       <c r="U8" t="n">
-        <v>-2.6829</v>
+        <v>-1.3633</v>
       </c>
       <c r="V8" t="n">
-        <v>0.532</v>
+        <v>0.3373</v>
       </c>
       <c r="W8" t="n">
-        <v>1.7384</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.2065</v>
+        <v>0.3373</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>R. SOLIVELLES MENDEZ</t>
+          <t>S. CASAÚ PUEYO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.8915</v>
+        <v>-1.8028</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.2371</v>
+        <v>-2.0471</v>
       </c>
       <c r="F9" t="n">
-        <v>0.3456</v>
+        <v>0.2444</v>
       </c>
       <c r="G9" t="n">
-        <v>0.3356</v>
+        <v>-1.273</v>
       </c>
       <c r="H9" t="n">
-        <v>0.7657</v>
+        <v>-2.8277</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.4302</v>
+        <v>1.5547</v>
       </c>
       <c r="J9" t="n">
-        <v>0.4949</v>
+        <v>-0.0774</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0053</v>
+        <v>-2.1308</v>
       </c>
       <c r="L9" t="n">
-        <v>0.4896</v>
+        <v>2.0533</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.1593</v>
+        <v>-1.1956</v>
       </c>
       <c r="N9" t="n">
-        <v>0.7604</v>
+        <v>-0.6969</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.9198</v>
+        <v>-0.4986</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.3968</v>
+        <v>-1.5871</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.9838</v>
+        <v>-5.9515</v>
       </c>
       <c r="R9" t="n">
-        <v>1.5871</v>
+        <v>4.3645</v>
       </c>
       <c r="S9" t="n">
-        <v>-2.1675</v>
+        <v>-2.2248</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.7481</v>
+        <v>0.0965</v>
       </c>
       <c r="U9" t="n">
-        <v>-1.4194</v>
+        <v>-2.3213</v>
       </c>
       <c r="V9" t="n">
-        <v>0.3373</v>
+        <v>3.2821</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>3.8854</v>
       </c>
       <c r="X9" t="n">
-        <v>0.3373</v>
+        <v>-0.6032</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>S. CASAÚ PUEYO</t>
+          <t>P. FEIXA MORANCHO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.9507</v>
+        <v>-1.8301</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.2512</v>
+        <v>1.3204</v>
       </c>
       <c r="F10" t="n">
-        <v>0.3005</v>
+        <v>-3.1504</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.273</v>
+        <v>3.2825</v>
       </c>
       <c r="H10" t="n">
-        <v>-2.8277</v>
+        <v>4.0818</v>
       </c>
       <c r="I10" t="n">
-        <v>1.5547</v>
+        <v>-0.7993</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.0774</v>
+        <v>3.3665</v>
       </c>
       <c r="K10" t="n">
-        <v>-2.1308</v>
+        <v>3.246</v>
       </c>
       <c r="L10" t="n">
-        <v>2.0533</v>
+        <v>0.1205</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.1956</v>
+        <v>-0.08400000000000001</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.6969</v>
+        <v>0.8358</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.4986</v>
+        <v>-0.9198</v>
       </c>
       <c r="P10" t="n">
-        <v>-1.5871</v>
+        <v>0.1984</v>
       </c>
       <c r="Q10" t="n">
-        <v>-5.9515</v>
+        <v>-1.9838</v>
       </c>
       <c r="R10" t="n">
-        <v>4.3645</v>
+        <v>2.1822</v>
       </c>
       <c r="S10" t="n">
-        <v>-2.3728</v>
+        <v>-1.7629</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.1076</v>
+        <v>-0.0623</v>
       </c>
       <c r="U10" t="n">
-        <v>-2.2652</v>
+        <v>-1.7006</v>
       </c>
       <c r="V10" t="n">
-        <v>3.2821</v>
+        <v>-3.5481</v>
       </c>
       <c r="W10" t="n">
-        <v>3.8854</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.6032</v>
+        <v>-3.5481</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.0942</v>
+        <v>-2.1044</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.1773</v>
+        <v>-1.0753</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.9169</v>
+        <v>-1.0291</v>
       </c>
       <c r="G11" t="n">
         <v>-1.8096</v>
@@ -1312,13 +1312,13 @@
         <v>1.1903</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.4829</v>
+        <v>-0.4931</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.1757</v>
+        <v>-0.0737</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.3072</v>
+        <v>-0.4195</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>4.640899999999998</v>
+        <v>4.952500000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>13.6969</v>
+        <v>14.0086</v>
       </c>
       <c r="F12" t="n">
-        <v>-9.056000000000001</v>
+        <v>-9.0558</v>
       </c>
       <c r="G12" t="n">
         <v>8.531100000000002</v>
@@ -1378,7 +1378,7 @@
         <v>-3.7881</v>
       </c>
       <c r="O12" t="n">
-        <v>-6.476999999999999</v>
+        <v>-6.477</v>
       </c>
       <c r="P12" t="n">
         <v>4.959700000000001</v>
@@ -1390,16 +1390,16 @@
         <v>24.7981</v>
       </c>
       <c r="S12" t="n">
-        <v>-15.2191</v>
+        <v>-14.9076</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.6715</v>
+        <v>-1.3596</v>
       </c>
       <c r="U12" t="n">
-        <v>-13.5479</v>
+        <v>-13.5481</v>
       </c>
       <c r="V12" t="n">
-        <v>6.369699999999999</v>
+        <v>6.3697</v>
       </c>
       <c r="W12" t="n">
         <v>16.4107</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>6.1104</v>
+        <v>4.268</v>
       </c>
       <c r="E13" t="n">
-        <v>7.4425</v>
+        <v>5.2999</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.3321</v>
+        <v>-1.0319</v>
       </c>
       <c r="G13" t="n">
         <v>-0.6251</v>
@@ -1468,13 +1468,13 @@
         <v>3.5709</v>
       </c>
       <c r="S13" t="n">
-        <v>4.9275</v>
+        <v>3.085</v>
       </c>
       <c r="T13" t="n">
-        <v>4.9995</v>
+        <v>2.8569</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.0721</v>
+        <v>0.228</v>
       </c>
       <c r="V13" t="n">
         <v>1.0145</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.1548</v>
+        <v>3.403</v>
       </c>
       <c r="E14" t="n">
-        <v>2.4372</v>
+        <v>3.6616</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.2824</v>
+        <v>-0.2586</v>
       </c>
       <c r="G14" t="n">
         <v>1.3361</v>
@@ -1546,13 +1546,13 @@
         <v>1.7855</v>
       </c>
       <c r="S14" t="n">
-        <v>0.1009</v>
+        <v>1.349</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.2153</v>
+        <v>1.009</v>
       </c>
       <c r="U14" t="n">
-        <v>0.3162</v>
+        <v>0.34</v>
       </c>
       <c r="V14" t="n">
         <v>-0.8692</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.4679</v>
+        <v>3.2951</v>
       </c>
       <c r="E15" t="n">
-        <v>2.2914</v>
+        <v>3.6178</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.8234</v>
+        <v>-0.3227</v>
       </c>
       <c r="G15" t="n">
         <v>2.0426</v>
@@ -1624,13 +1624,13 @@
         <v>2.1822</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.8508</v>
+        <v>0.9764</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.4761</v>
+        <v>0.8502999999999999</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.3747</v>
+        <v>0.1261</v>
       </c>
       <c r="V15" t="n">
         <v>-0.1206</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.4559</v>
+        <v>2.0459</v>
       </c>
       <c r="E16" t="n">
-        <v>3.251</v>
+        <v>3.7611</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.7951</v>
+        <v>-1.7152</v>
       </c>
       <c r="G16" t="n">
         <v>-2.1902</v>
@@ -1702,13 +1702,13 @@
         <v>2.579</v>
       </c>
       <c r="S16" t="n">
-        <v>1.2493</v>
+        <v>1.8394</v>
       </c>
       <c r="T16" t="n">
-        <v>0.8333</v>
+        <v>1.3435</v>
       </c>
       <c r="U16" t="n">
-        <v>0.416</v>
+        <v>0.4959</v>
       </c>
       <c r="V16" t="n">
         <v>1.2065</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>P. FLUXA PAYERAS</t>
+          <t>H. MORRO BALERA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.4426</v>
+        <v>-0.8852</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.3106</v>
+        <v>-0.1581</v>
       </c>
       <c r="F17" t="n">
-        <v>0.868</v>
+        <v>-0.7271</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.3307</v>
+        <v>-0.6284999999999999</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.8568</v>
+        <v>-0.2269</v>
       </c>
       <c r="I17" t="n">
-        <v>0.526</v>
+        <v>-0.4016</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.0912</v>
+        <v>0.0403</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.3321</v>
+        <v>0.0403</v>
       </c>
       <c r="L17" t="n">
-        <v>0.241</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.2395</v>
+        <v>-0.6688</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.5246</v>
+        <v>-0.2672</v>
       </c>
       <c r="O17" t="n">
-        <v>0.2851</v>
+        <v>-0.4016</v>
       </c>
       <c r="P17" t="n">
-        <v>-3.1741</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>-4.1661</v>
+        <v>-0.1984</v>
       </c>
       <c r="R17" t="n">
-        <v>0.9919</v>
+        <v>0.1984</v>
       </c>
       <c r="S17" t="n">
-        <v>1.8558</v>
+        <v>-0.136</v>
       </c>
       <c r="T17" t="n">
-        <v>1.7402</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>0.1156</v>
+        <v>-0.136</v>
       </c>
       <c r="V17" t="n">
-        <v>1.2065</v>
+        <v>-0.1206</v>
       </c>
       <c r="W17" t="n">
-        <v>1.2065</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-0.1206</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>M. OCHOGAVIA CIFRE</t>
+          <t>P. FLUXA PAYERAS</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.7027</v>
+        <v>-0.8984</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.7465</v>
+        <v>-2.1268</v>
       </c>
       <c r="F18" t="n">
-        <v>1.0438</v>
+        <v>1.2284</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.3132</v>
+        <v>-0.3307</v>
       </c>
       <c r="H18" t="n">
-        <v>0.4433</v>
+        <v>-0.8568</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.7566000000000001</v>
+        <v>0.526</v>
       </c>
       <c r="J18" t="n">
-        <v>0.141</v>
+        <v>-0.0912</v>
       </c>
       <c r="K18" t="n">
-        <v>0.1008</v>
+        <v>-0.3321</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0402</v>
+        <v>0.241</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.4542</v>
+        <v>-0.2395</v>
       </c>
       <c r="N18" t="n">
-        <v>0.3425</v>
+        <v>-0.5246</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.7967</v>
+        <v>0.2851</v>
       </c>
       <c r="P18" t="n">
-        <v>-1.1903</v>
+        <v>-3.1741</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.3806</v>
+        <v>-4.1661</v>
       </c>
       <c r="R18" t="n">
-        <v>1.1903</v>
+        <v>0.9919</v>
       </c>
       <c r="S18" t="n">
-        <v>1.1874</v>
+        <v>1.4</v>
       </c>
       <c r="T18" t="n">
-        <v>0.4932</v>
+        <v>0.924</v>
       </c>
       <c r="U18" t="n">
-        <v>0.6943</v>
+        <v>0.4761</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.3866</v>
+        <v>1.2065</v>
       </c>
       <c r="W18" t="n">
+        <v>1.2065</v>
+      </c>
+      <c r="X18" t="n">
         <v>0</v>
-      </c>
-      <c r="X18" t="n">
-        <v>-0.3866</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>H. MORRO BALERA</t>
+          <t>M. OCHOGAVIA CIFRE</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.8852</v>
+        <v>-0.9875</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.1581</v>
+        <v>-1.7465</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.7271</v>
+        <v>0.759</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.6284999999999999</v>
+        <v>-0.3132</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.2269</v>
+        <v>0.4433</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.4016</v>
+        <v>-0.7566000000000001</v>
       </c>
       <c r="J19" t="n">
-        <v>0.0403</v>
+        <v>0.141</v>
       </c>
       <c r="K19" t="n">
-        <v>0.0403</v>
+        <v>0.1008</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>0.0402</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.6688</v>
+        <v>-0.4542</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.2672</v>
+        <v>0.3425</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.4016</v>
+        <v>-0.7967</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>-1.1903</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.1984</v>
+        <v>-2.3806</v>
       </c>
       <c r="R19" t="n">
-        <v>0.1984</v>
+        <v>1.1903</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.136</v>
+        <v>0.9026</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>0.4932</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.136</v>
+        <v>0.4095</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.1206</v>
+        <v>-0.3866</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.1206</v>
+        <v>-0.3866</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.2752</v>
+        <v>-1.4274</v>
       </c>
       <c r="E20" t="n">
-        <v>1.0779</v>
+        <v>0.8738</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.3531</v>
+        <v>-2.3012</v>
       </c>
       <c r="G20" t="n">
         <v>-2.5099</v>
@@ -2014,13 +2014,13 @@
         <v>2.7774</v>
       </c>
       <c r="S20" t="n">
-        <v>2.5286</v>
+        <v>2.3764</v>
       </c>
       <c r="T20" t="n">
-        <v>2.3298</v>
+        <v>2.1257</v>
       </c>
       <c r="U20" t="n">
-        <v>0.1989</v>
+        <v>0.2507</v>
       </c>
       <c r="V20" t="n">
         <v>-2.4842</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.9524</v>
+        <v>-3.6733</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.6499</v>
+        <v>-2.0581</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.3024</v>
+        <v>-1.6153</v>
       </c>
       <c r="G21" t="n">
         <v>-3.5211</v>
@@ -2092,13 +2092,13 @@
         <v>1.1903</v>
       </c>
       <c r="S21" t="n">
-        <v>2.9655</v>
+        <v>2.2446</v>
       </c>
       <c r="T21" t="n">
-        <v>1.8026</v>
+        <v>1.3944</v>
       </c>
       <c r="U21" t="n">
-        <v>1.163</v>
+        <v>0.8501</v>
       </c>
       <c r="V21" t="n">
         <v>-1.2065</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.1939</v>
+        <v>-3.7773</v>
       </c>
       <c r="E22" t="n">
         <v>-1.8427</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.3513</v>
+        <v>-1.9347</v>
       </c>
       <c r="G22" t="n">
         <v>-1.7762</v>
@@ -2170,13 +2170,13 @@
         <v>1.3887</v>
       </c>
       <c r="S22" t="n">
-        <v>0.7029</v>
+        <v>1.1195</v>
       </c>
       <c r="T22" t="n">
         <v>1.1961</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.4932</v>
+        <v>-0.0766</v>
       </c>
       <c r="V22" t="n">
         <v>-1.9303</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.3779</v>
+        <v>-4.6434</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.7363</v>
+        <v>-0.2262</v>
       </c>
       <c r="F23" t="n">
-        <v>-4.6416</v>
+        <v>-4.4172</v>
       </c>
       <c r="G23" t="n">
         <v>-0.0147</v>
@@ -2248,13 +2248,13 @@
         <v>1.9838</v>
       </c>
       <c r="S23" t="n">
-        <v>0.6882</v>
+        <v>1.4228</v>
       </c>
       <c r="T23" t="n">
-        <v>0.8447</v>
+        <v>1.3548</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.1565</v>
+        <v>0.0679</v>
       </c>
       <c r="V23" t="n">
         <v>-2.6789</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.6409</v>
+        <v>-3.280499999999998</v>
       </c>
       <c r="E24" t="n">
-        <v>9.055899999999999</v>
+        <v>9.055800000000001</v>
       </c>
       <c r="F24" t="n">
-        <v>-13.6967</v>
+        <v>-12.3365</v>
       </c>
       <c r="G24" t="n">
         <v>-8.530899999999999</v>
@@ -2326,13 +2326,13 @@
         <v>19.8384</v>
       </c>
       <c r="S24" t="n">
-        <v>15.2193</v>
+        <v>16.5797</v>
       </c>
       <c r="T24" t="n">
-        <v>13.548</v>
+        <v>13.5479</v>
       </c>
       <c r="U24" t="n">
-        <v>1.6715</v>
+        <v>3.031699999999999</v>
       </c>
       <c r="V24" t="n">
         <v>-6.369400000000001</v>
